--- a/results/sample-mock-run/benchmark_results.xlsx
+++ b/results/sample-mock-run/benchmark_results.xlsx
@@ -8,28 +8,30 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summarization" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hallucination" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classification" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CrossLingual" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SurfaceFacts" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cost" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Usage" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Judge" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runs" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summarization" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hallucination" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classification" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CrossLingual" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SurfaceFacts" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cost" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Usage" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Judge" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runs" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Leaderboard'!$A$1:$AK$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Summarization'!$A$1:$P$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Hallucination'!$A$1:$O$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Classification'!$A$1:$I$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'CrossLingual'!$A$1:$M$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'SurfaceFacts'!$A$1:$L$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Cost'!$A$1:$S$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Usage'!$A$1:$M$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Judge'!$A$1:$A$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Runs'!$A$1:$T$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Legend'!$A$1:$D$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Leaderboard'!$A$1:$AK$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Summarization'!$A$1:$P$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Hallucination'!$A$1:$O$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Classification'!$A$1:$I$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'CrossLingual'!$A$1:$M$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'SurfaceFacts'!$A$1:$L$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Cost'!$A$1:$S$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Usage'!$A$1:$M$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Judge'!$A$1:$A$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Runs'!$A$1:$T$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -512,7 +514,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T04:09:37+00:00</t>
+          <t>2026-09-16T04:48:12+00:00</t>
         </is>
       </c>
     </row>
@@ -601,6 +603,34 @@
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Mean the metric was not computed (e.g. BERTScore extra not installed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Metric directions</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>↑ 높을수록 좋음 · ↓ 낮을수록 좋음 · — 좋고 나쁨이 아니라 해석용</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Legend sheet</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Explains every metric column: what it means and which way is better.</t>
         </is>
       </c>
     </row>
@@ -610,6 +640,148 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>display_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>successful_cases</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>prompt_tokens</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>cached_tokens</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>cache_write_tokens</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>completion_tokens</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>reasoning_tokens</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>total_tokens</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>cache_hits</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>cache_misses</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>openrouter_api_calls</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>openrouter_http_attempts</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>google/gemini-2.5-flash-lite</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>844524</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>24718</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>869242</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="K2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:M2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -634,7 +806,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -780,17 +952,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>run-20260916T040949-8060316b</t>
+          <t>run-20260916T044826-3b4b236c</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T04:09:51+00:00</t>
+          <t>2026-09-16T04:48:28+00:00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-16T04:09:49+00:00</t>
+          <t>2026-09-16T04:48:26+00:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -800,7 +972,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1a5b74b324b529b0e48679bff73ef485a6d623f3</t>
+          <t>8d709c8d679a9226e30d04c8bb8a4757529688a6</t>
         </is>
       </c>
       <c r="H2" t="b">
@@ -860,6 +1032,1193 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D53"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="90" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Sheet</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>지표</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>방향</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>의미</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Summarization</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Cases</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>채점 대상 케이스 수.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Summarization</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ROUGE-Lsum</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>참조 요약과의 최장 공통 부분열 기반 F1 (0~1). 문장 단위로 계산. 한국어는 문자 단위 토큰화라 영어 값과 직접 비교 불가.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Summarization</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>chrF++</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>문자 n-gram + 단어 bigram F-score (0~100). 어형 변화에 강해 한국어에 비교적 공정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Summarization</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BERTScore</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>다국어 임베딩 기반 의미 유사도 F1 (0~1). 표현이 달라도 뜻이 같으면 점수를 줍니다. 선택 설치.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Summarization</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Surface facts</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>요약에서 뽑은 표면적 사실 중 원문에서 확인되는 비율 (0~1). 진단 지표.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Summarization</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Compression</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>출력 길이 ÷ 원문 길이. 낮으면 압축적, 높으면 장황. 낮다고 무조건 좋은 것은 아닙니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Summarization</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Out tokens</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>평균 출력 길이(추정 토큰).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Summarization</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Empty</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>빈 출력 비율.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Summarization</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Refusal</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>거부 응답 비율. 빈 출력과 거부는 분모에서 빼지 않습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Hallucination</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>`OK` 또는 `SKIPPED`(해당 언어 데이터 미준비).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Hallucination</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Cases</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>케이스 수. 문서 수 × 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Hallucination</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>전체 정답률 (0~1). 레이블이 반반이므로 0.5가 무작위 수준.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Hallucination</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Macro-F1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>두 레이블 F1의 단순 평균 (0~1). 한쪽 레이블만 찍는 모델을 걸러냅니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Hallucination</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Halu P</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>HALLUCINATED 라고 답한 것 중 실제로 맞은 비율. 낮으면 멀쩡한 요약을 환각이라고 의심.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Hallucination</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Halu R</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>실제 HALLUCINATED 중 잡아낸 비율. 낮으면 환각을 놓침.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Hallucination</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Halu F1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Halu P 와 Halu R 의 조화평균. 환각 탐지 성능의 대표값.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Hallucination</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Supported R</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>실제 SUPPORTED 중 맞힌 비율. 이 값만 낮으면 과도하게 의심하는 모델.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Hallucination</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Invalid</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>레이블로 파싱할 수 없는 출력 비율. **오답으로 계산됩니다.**</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>`en` / `ko` / `overall`(두 언어 합산).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Cases</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>분류한 발화 수.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>정답률 (0~1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Macro-F1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>60개 인텐트별 F1의 평균 (0~1). 드문 인텐트를 무시하는 모델에 불리하게 작동합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Invalid</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>형식을 못 지켜 답을 못 읽은 비율. 오답으로 계산됩니다. 배치 형식을 못 지키면 여기가 올라갑니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CrossLingual</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Pairs</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>비교한 EN/KO 쌍의 수.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CrossLingual</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Consistency</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>두 언어에서 정오답이 일치한 비율(둘 다 맞음 + 둘 다 틀림). 높을수록 언어에 따라 흔들리지 않음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CrossLingual</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Pred. agreement</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>정답 여부와 무관하게 **같은 인텐트** 를 예측한 비율. 정확도와 분리된 안정성 지표.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CrossLingual</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Both correct</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>두 언어 모두 맞힌 비율.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CrossLingual</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>EN only</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>영어만 맞힌 비율. 높으면 한국어가 약함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CrossLingual</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>KO only</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>한국어만 맞힌 비율. 높으면 영어가 약함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CrossLingual</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Both wrong</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>두 언어 모두 틀린 비율.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SurfaceFacts</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Facts</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>요약에서 추출된 사실의 총 개수. 적으면 아래 비율의 신뢰도가 낮습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SurfaceFacts</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>그중 원문에서 확인된 비율 (0~1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SurfaceFacts</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>원문에 없는 숫자 건수.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SurfaceFacts</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Percent</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>원문과 다른 백분율 건수. (원문 12% → 요약 21% 같은 경우)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SurfaceFacts</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>원문에 없는 날짜 건수.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SurfaceFacts</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>원문에 없는 금액 건수.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SurfaceFacts</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>원문에 없는 고유명사 건수.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Summarization / Hallucination / Classification</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>벤치마크별 누적 청구액.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Retry/error</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>실패했지만 과금된 시도의 합. 0이 아니면 재시도가 돈을 쓴 것.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Judge</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>LLM-as-a-Judge 비용. 기본 예산과 별도로 집계합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>이 모델 캐시를 만드는 데 지금까지 지불한 총액.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Fresh this run</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>마지막 실행에서 **새로** 청구된 금액. 캐시가 다 맞으면 $0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Cache savings</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>캐시 덕분에 다시 내지 않은 금액.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Usage</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Cases</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>성공적으로 저장된 케이스 수.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Usage</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Prompt / Completion / Total</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>입력·출력·합계 토큰.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Usage</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Cached</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>프롬프트 캐시로 할인된 입력 토큰.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Usage</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Reasoning</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>thinking 토큰. thinking 을 끌 수 없는 모델만 0이 아닙니다. 과금 대상입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Usage</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>API calls</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>실제로 OpenRouter 로 나간 요청 수. 재실행에서 0이면 캐시가 완전히 맞은 것.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Usage</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Cache hits</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>캐시로 처리해 요청하지 않은 수.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Judge</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Self-judge</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>`예` 면 모델이 자기 출력을 채점한 것. 신뢰하지 마세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Judge</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Factual / Coverage / Conciseness / Overall</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>각 1~5 정수 채점의 평균.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Judge</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Judge cost</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>judge 호출의 실제 청구액.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D53"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1131,7 +2490,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-16T04:09:48+00:00</t>
+          <t>2026-09-16T04:48:25+00:00</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -1223,7 +2582,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1446,7 +2805,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1665,7 +3024,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1843,7 +3202,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1985,7 +3344,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2164,7 +3523,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2318,7 +3677,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-16T04:09:48+00:00</t>
+          <t>2026-09-16T04:48:25+00:00</t>
         </is>
       </c>
       <c r="H2" s="3" t="n">
@@ -2362,146 +3721,4 @@
   <autoFilter ref="A1:S2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="26" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>display_name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>successful_cases</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>prompt_tokens</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>cached_tokens</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>cache_write_tokens</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>completion_tokens</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>reasoning_tokens</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>total_tokens</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>cache_hits</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>cache_misses</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>openrouter_api_calls</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>openrouter_http_attempts</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>google/gemini-2.5-flash-lite</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Gemini 2.5 Flash-Lite</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="D2" s="5" t="n">
-        <v>844524</v>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>24718</v>
-      </c>
-      <c r="H2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="5" t="n">
-        <v>869242</v>
-      </c>
-      <c r="J2" s="5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="K2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:M2"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/results/sample-mock-run/benchmark_results.xlsx
+++ b/results/sample-mock-run/benchmark_results.xlsx
@@ -14,24 +14,26 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hallucination" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classification" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CrossLingual" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SurfaceFacts" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cost" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Usage" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Judge" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runs" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ClassificationModes" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SurfaceFacts" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cost" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Usage" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Judge" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runs" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Legend'!$A$1:$D$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Legend'!$A$1:$D$59</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Leaderboard'!$A$1:$AK$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Summarization'!$A$1:$P$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Hallucination'!$A$1:$O$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Classification'!$A$1:$I$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'CrossLingual'!$A$1:$M$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'SurfaceFacts'!$A$1:$L$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Cost'!$A$1:$S$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Usage'!$A$1:$M$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Judge'!$A$1:$A$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Runs'!$A$1:$T$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'ClassificationModes'!$A$1:$A$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'SurfaceFacts'!$A$1:$L$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cost'!$A$1:$S$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Usage'!$A$1:$M$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Judge'!$A$1:$A$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Runs'!$A$1:$T$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -514,7 +516,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T04:48:12+00:00</t>
+          <t>2026-09-17T00:38:37+00:00</t>
         </is>
       </c>
     </row>
@@ -640,6 +642,206 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:S2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="25" customWidth="1" min="17" max="17"/>
+    <col width="31" customWidth="1" min="18" max="18"/>
+    <col width="19" customWidth="1" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>display_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>input_per_million</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>cached_input_per_million</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>output_per_million</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>pricing_source</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>pricing_retrieved_at</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>summarization_cost</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>hallucination_cost</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>classification_cost</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>retry_error_cost</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>judge_cost</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>total_openrouter_cost</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>fresh_cost_this_run</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>stored_benchmark_cost</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_without_cache</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cache_savings</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>recomputed_from_pricing_table</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>reconciliation_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>google/gemini-2.5-flash-lite</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>openrouter</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-09-17T00:38:49+00:00</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>0.0319042</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>0.0562255</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0.0062099</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>0.0943396</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>0.0943396</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>0.09433960000000008</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.09433960000000008</v>
+      </c>
+      <c r="R2" s="4" t="n">
+        <v>0.09433960000000001</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:S2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -781,7 +983,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -806,7 +1008,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -952,17 +1154,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>run-20260916T044826-3b4b236c</t>
+          <t>run-20260917T003850-a08557e6</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T04:48:28+00:00</t>
+          <t>2026-09-17T00:38:52+00:00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-16T04:48:26+00:00</t>
+          <t>2026-09-17T00:38:50+00:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -972,7 +1174,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>8d709c8d679a9226e30d04c8bb8a4757529688a6</t>
+          <t>259eab707098181699d06f21498431115d9b9625</t>
         </is>
       </c>
       <c r="H2" t="b">
@@ -1037,10 +1239,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
     <col width="46" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="90" customWidth="1" min="4" max="4"/>
@@ -1577,34 +1779,34 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CrossLingual</t>
+          <t>ClassificationModes</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Pairs</t>
+          <t>text / json_schema Acc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>비교한 EN/KO 쌍의 수.</t>
+          <t>각 조건의 정확도.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CrossLingual</t>
+          <t>ClassificationModes</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Consistency</t>
+          <t>Δ Acc</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1614,19 +1816,19 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>두 언어에서 정오답이 일치한 비율(둘 다 맞음 + 둘 다 틀림). 높을수록 언어에 따라 흔들리지 않음.</t>
+          <t>json_schema − text. 양수면 제약을 걸었을 때 올라간 것.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CrossLingual</t>
+          <t>ClassificationModes</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Pred. agreement</t>
+          <t>text / json_schema F1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1636,19 +1838,19 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>정답 여부와 무관하게 **같은 인텐트** 를 예측한 비율. 정확도와 분리된 안정성 지표.</t>
+          <t>각 조건의 macro-F1.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CrossLingual</t>
+          <t>ClassificationModes</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Both correct</t>
+          <t>Δ F1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1658,19 +1860,19 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>두 언어 모두 맞힌 비율.</t>
+          <t>macro-F1 차이.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CrossLingual</t>
+          <t>ClassificationModes</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>EN only</t>
+          <t>text / json_schema Inv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1680,19 +1882,19 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>영어만 맞힌 비율. 높으면 한국어가 약함.</t>
+          <t>각 조건의 invalid 비율.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CrossLingual</t>
+          <t>ClassificationModes</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>KO only</t>
+          <t>Δ Inv</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1702,7 +1904,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>한국어만 맞힌 비율. 높으면 영어가 약함.</t>
+          <t>invalid 비율 차이. 제약이 걸리면 보통 0 으로 떨어집니다.</t>
         </is>
       </c>
     </row>
@@ -1714,51 +1916,51 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Both wrong</t>
+          <t>Pairs</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>두 언어 모두 틀린 비율.</t>
+          <t>비교한 EN/KO 쌍의 수.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SurfaceFacts</t>
+          <t>CrossLingual</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Facts</t>
+          <t>Consistency</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>요약에서 추출된 사실의 총 개수. 적으면 아래 비율의 신뢰도가 낮습니다.</t>
+          <t>두 언어에서 정오답이 일치한 비율(둘 다 맞음 + 둘 다 틀림). 높을수록 언어에 따라 흔들리지 않음.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SurfaceFacts</t>
+          <t>CrossLingual</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Pred. agreement</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1768,41 +1970,41 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>그중 원문에서 확인된 비율 (0~1).</t>
+          <t>정답 여부와 무관하게 **같은 인텐트** 를 예측한 비율. 정확도와 분리된 안정성 지표.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SurfaceFacts</t>
+          <t>CrossLingual</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Both correct</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>원문에 없는 숫자 건수.</t>
+          <t>두 언어 모두 맞힌 비율.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SurfaceFacts</t>
+          <t>CrossLingual</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Percent</t>
+          <t>EN only</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1812,19 +2014,19 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>원문과 다른 백분율 건수. (원문 12% → 요약 21% 같은 경우)</t>
+          <t>영어만 맞힌 비율. 높으면 한국어가 약함.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SurfaceFacts</t>
+          <t>CrossLingual</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>KO only</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1834,19 +2036,19 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>원문에 없는 날짜 건수.</t>
+          <t>한국어만 맞힌 비율. 높으면 영어가 약함.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SurfaceFacts</t>
+          <t>CrossLingual</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>Both wrong</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1856,7 +2058,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>원문에 없는 금액 건수.</t>
+          <t>두 언어 모두 틀린 비율.</t>
         </is>
       </c>
     </row>
@@ -1868,51 +2070,51 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Entity</t>
+          <t>Facts</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>원문에 없는 고유명사 건수.</t>
+          <t>요약에서 추출된 사실의 총 개수. 적으면 아래 비율의 신뢰도가 낮습니다.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cost</t>
+          <t>SurfaceFacts</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Summarization / Hallucination / Classification</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>벤치마크별 누적 청구액.</t>
+          <t>그중 원문에서 확인된 비율 (0~1).</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cost</t>
+          <t>SurfaceFacts</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Retry/error</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1922,19 +2124,19 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>실패했지만 과금된 시도의 합. 0이 아니면 재시도가 돈을 쓴 것.</t>
+          <t>원문에 없는 숫자 건수.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cost</t>
+          <t>SurfaceFacts</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Judge</t>
+          <t>Percent</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1944,19 +2146,19 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>LLM-as-a-Judge 비용. 기본 예산과 별도로 집계합니다.</t>
+          <t>원문과 다른 백분율 건수. (원문 12% → 요약 21% 같은 경우)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cost</t>
+          <t>SurfaceFacts</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1966,173 +2168,173 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>이 모델 캐시를 만드는 데 지금까지 지불한 총액.</t>
+          <t>원문에 없는 날짜 건수.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cost</t>
+          <t>SurfaceFacts</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Fresh this run</t>
+          <t>Currency</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>마지막 실행에서 **새로** 청구된 금액. 캐시가 다 맞으면 $0.</t>
+          <t>원문에 없는 금액 건수.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cost</t>
+          <t>SurfaceFacts</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cache savings</t>
+          <t>Entity</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>캐시 덕분에 다시 내지 않은 금액.</t>
+          <t>원문에 없는 고유명사 건수.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Usage</t>
+          <t>Cost</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cases</t>
+          <t>Summarization / Hallucination / Classification</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>성공적으로 저장된 케이스 수.</t>
+          <t>벤치마크별 누적 청구액.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Usage</t>
+          <t>Cost</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Prompt / Completion / Total</t>
+          <t>Retry/error</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>입력·출력·합계 토큰.</t>
+          <t>실패했지만 과금된 시도의 합. 0이 아니면 재시도가 돈을 쓴 것.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Usage</t>
+          <t>Cost</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cached</t>
+          <t>Judge</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>프롬프트 캐시로 할인된 입력 토큰.</t>
+          <t>LLM-as-a-Judge 비용. 기본 예산과 별도로 집계합니다.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Usage</t>
+          <t>Cost</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Reasoning</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>thinking 토큰. thinking 을 끌 수 없는 모델만 0이 아닙니다. 과금 대상입니다.</t>
+          <t>이 모델 캐시를 만드는 데 지금까지 지불한 총액.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Usage</t>
+          <t>Cost</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>API calls</t>
+          <t>Fresh this run</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>실제로 OpenRouter 로 나간 요청 수. 재실행에서 0이면 캐시가 완전히 맞은 것.</t>
+          <t>마지막 실행에서 **새로** 청구된 금액. 캐시가 다 맞으면 $0.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Usage</t>
+          <t>Cost</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cache hits</t>
+          <t>Cache savings</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2142,78 +2344,210 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>캐시로 처리해 요청하지 않은 수.</t>
+          <t>캐시 덕분에 다시 내지 않은 금액.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Judge</t>
+          <t>Usage</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Self-judge</t>
+          <t>Cases</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>`예` 면 모델이 자기 출력을 채점한 것. 신뢰하지 마세요.</t>
+          <t>성공적으로 저장된 케이스 수.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Judge</t>
+          <t>Usage</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Factual / Coverage / Conciseness / Overall</t>
+          <t>Prompt / Completion / Total</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>각 1~5 정수 채점의 평균.</t>
+          <t>입력·출력·합계 토큰.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>Usage</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Cached</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>프롬프트 캐시로 할인된 입력 토큰.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Usage</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Reasoning</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>thinking 토큰. thinking 을 끌 수 없는 모델만 0이 아닙니다. 과금 대상입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Usage</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>API calls</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>실제로 OpenRouter 로 나간 요청 수. 재실행에서 0이면 캐시가 완전히 맞은 것.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Usage</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Cache hits</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>캐시로 처리해 요청하지 않은 수.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>Judge</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Self-judge</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>`예` 면 모델이 자기 출력을 채점한 것. 신뢰하지 마세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Judge</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Factual / Coverage / Conciseness / Overall</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>각 1~5 정수 채점의 평균.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Judge</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
         <is>
           <t>Judge cost</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>judge 호출의 실제 청구액.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D53"/>
+  <autoFilter ref="A1:D59"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2490,7 +2824,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-16T04:48:25+00:00</t>
+          <t>2026-09-17T00:38:49+00:00</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -3350,6 +3684,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:A1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3521,204 +3880,4 @@
   <autoFilter ref="A1:L3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:S2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="27" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="23" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
-    <col width="23" customWidth="1" min="15" max="15"/>
-    <col width="30" customWidth="1" min="16" max="16"/>
-    <col width="25" customWidth="1" min="17" max="17"/>
-    <col width="31" customWidth="1" min="18" max="18"/>
-    <col width="19" customWidth="1" min="19" max="19"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>display_name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>input_per_million</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>cached_input_per_million</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>output_per_million</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>pricing_source</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>pricing_retrieved_at</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>summarization_cost</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>hallucination_cost</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>classification_cost</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>retry_error_cost</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>judge_cost</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>total_openrouter_cost</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>fresh_cost_this_run</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>stored_benchmark_cost</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>estimated_cost_without_cache</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>estimated_cache_savings</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>recomputed_from_pricing_table</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>reconciliation_ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>google/gemini-2.5-flash-lite</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Gemini 2.5 Flash-Lite</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>openrouter</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2026-09-16T04:48:25+00:00</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>0.0319042</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>0.0562255</v>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>0.0062099</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="3" t="n">
-        <v>0.0943396</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>0.0943396</v>
-      </c>
-      <c r="P2" s="3" t="n">
-        <v>0.09433960000000008</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.09433960000000008</v>
-      </c>
-      <c r="R2" s="4" t="n">
-        <v>0.09433960000000001</v>
-      </c>
-      <c r="S2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:S2"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/results/sample-mock-run/benchmark_results.xlsx
+++ b/results/sample-mock-run/benchmark_results.xlsx
@@ -23,7 +23,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Legend'!$A$1:$D$59</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Leaderboard'!$A$1:$AK$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Leaderboard'!$A$1:$AL$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Summarization'!$A$1:$P$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Hallucination'!$A$1:$O$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Classification'!$A$1:$I$4</definedName>
@@ -516,7 +516,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:38:37+00:00</t>
+          <t>2026-09-17T01:56:09+00:00</t>
         </is>
       </c>
     </row>
@@ -795,7 +795,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:38:49+00:00</t>
+          <t>2026-09-17T01:56:21+00:00</t>
         </is>
       </c>
       <c r="H2" s="3" t="n">
@@ -1154,17 +1154,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>run-20260917T003850-a08557e6</t>
+          <t>run-20260917T015622-8a4a3258</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T00:38:52+00:00</t>
+          <t>2026-09-17T01:56:24+00:00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:38:50+00:00</t>
+          <t>2026-09-17T01:56:22+00:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>259eab707098181699d06f21498431115d9b9625</t>
+          <t>7d940a780adb2d63730876016bcc16115c9bd8e2</t>
         </is>
       </c>
       <c r="H2" t="b">
@@ -2558,46 +2558,47 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK2"/>
+  <dimension ref="A1:AL2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="27" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="19" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="19" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
     <col width="26" customWidth="1" min="17" max="17"/>
-    <col width="21" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="26" customWidth="1" min="18" max="18"/>
+    <col width="21" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
     <col width="18" customWidth="1" min="21" max="21"/>
-    <col width="16" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
     <col width="10" customWidth="1" min="24" max="24"/>
-    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="10" customWidth="1" min="25" max="25"/>
     <col width="22" customWidth="1" min="26" max="26"/>
     <col width="22" customWidth="1" min="27" max="27"/>
     <col width="22" customWidth="1" min="28" max="28"/>
-    <col width="19" customWidth="1" min="29" max="29"/>
-    <col width="14" customWidth="1" min="30" max="30"/>
-    <col width="15" customWidth="1" min="31" max="31"/>
+    <col width="22" customWidth="1" min="29" max="29"/>
+    <col width="19" customWidth="1" min="30" max="30"/>
+    <col width="14" customWidth="1" min="31" max="31"/>
     <col width="15" customWidth="1" min="32" max="32"/>
-    <col width="18" customWidth="1" min="33" max="33"/>
-    <col width="17" customWidth="1" min="34" max="34"/>
-    <col width="12" customWidth="1" min="35" max="35"/>
-    <col width="21" customWidth="1" min="36" max="36"/>
-    <col width="25" customWidth="1" min="37" max="37"/>
+    <col width="15" customWidth="1" min="33" max="33"/>
+    <col width="18" customWidth="1" min="34" max="34"/>
+    <col width="17" customWidth="1" min="35" max="35"/>
+    <col width="12" customWidth="1" min="36" max="36"/>
+    <col width="21" customWidth="1" min="37" max="37"/>
+    <col width="25" customWidth="1" min="38" max="38"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2618,170 +2619,175 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>api_provider</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>status</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>input_per_million</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>output_per_million</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>cached_input_per_million</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>pricing_source</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>pricing_retrieved_at</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>summary_en</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>summary_ko</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>summary_en_chrf</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>summary_ko_chrf</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>summary_en_bertscore</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>summary_ko_bertscore</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>summary_en_surface_facts</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>summary_ko_surface_facts</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>halu_en_f1</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>halu_ko_f1</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>halu_en_accuracy</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>halu_ko_accuracy</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>halu_ko_status</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>cls_en</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>cls_ko</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>cls_en_macro_f1</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>cls_ko_macro_f1</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>cls_overall_accuracy</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>cls_overall_macro_f1</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>en_ko_consistency</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>input_tokens</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>output_tokens</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>cached_tokens</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>reasoning_tokens</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>openrouter_cost</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>judge_cost</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>fresh_cost_this_run</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>estimated_cache_savings</t>
         </is>
@@ -2805,113 +2811,118 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>openrouter</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="G2" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="H2" s="3" t="n">
         <v>0.025</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>openrouter</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2026-09-17T00:38:49+00:00</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2026-09-17T01:56:21+00:00</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
         <v>0.1400999007733846</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>0.2298023292910851</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>22.50120530699853</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>12.4256821743804</v>
       </c>
-      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" s="4" t="n">
         <v>1</v>
       </c>
       <c r="R2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" s="4" t="n">
         <v>0.4603580562659846</v>
       </c>
-      <c r="S2" s="4" t="n">
+      <c r="T2" s="4" t="n">
         <v>0.5352798053527982</v>
       </c>
-      <c r="T2" s="4" t="n">
+      <c r="U2" s="4" t="n">
         <v>0.4725</v>
       </c>
-      <c r="U2" s="4" t="n">
+      <c r="V2" s="4" t="n">
         <v>0.5225</v>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>0.008</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Y2" t="n">
         <v>0.013</v>
       </c>
-      <c r="Y2" s="4" t="n">
+      <c r="Z2" s="4" t="n">
         <v>0.008084469907191399</v>
       </c>
-      <c r="Z2" s="4" t="n">
+      <c r="AA2" s="4" t="n">
         <v>0.01213267397278515</v>
       </c>
-      <c r="AA2" s="4" t="n">
+      <c r="AB2" s="4" t="n">
         <v>0.0105</v>
       </c>
-      <c r="AB2" s="4" t="n">
+      <c r="AC2" s="4" t="n">
         <v>0.009928959146388881</v>
       </c>
-      <c r="AC2" s="4" t="n">
+      <c r="AD2" s="4" t="n">
         <v>0.979</v>
       </c>
-      <c r="AD2" s="5" t="n">
+      <c r="AE2" s="5" t="n">
         <v>844524</v>
       </c>
-      <c r="AE2" s="5" t="n">
+      <c r="AF2" s="5" t="n">
         <v>24718</v>
-      </c>
-      <c r="AF2" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="AG2" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AH2" s="3" t="n">
+      <c r="AH2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" s="3" t="n">
         <v>0.0943396</v>
-      </c>
-      <c r="AI2" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="AJ2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" s="3" t="n">
         <v>0.09433960000000008</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK2"/>
+  <autoFilter ref="A1:AL2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/results/sample-mock-run/benchmark_results.xlsx
+++ b/results/sample-mock-run/benchmark_results.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:56:09+00:00</t>
+          <t>2026-09-17T03:05:01+00:00</t>
         </is>
       </c>
     </row>
@@ -795,7 +795,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:56:21+00:00</t>
+          <t>2026-09-17T03:05:14+00:00</t>
         </is>
       </c>
       <c r="H2" s="3" t="n">
@@ -1154,17 +1154,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>run-20260917T015622-8a4a3258</t>
+          <t>run-20260917T030515-f5f4b29b</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T01:56:24+00:00</t>
+          <t>2026-09-17T03:05:17+00:00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:56:22+00:00</t>
+          <t>2026-09-17T03:05:16+00:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>7d940a780adb2d63730876016bcc16115c9bd8e2</t>
+          <t>62bd51cc58aff3b5128149c0e7098fc7bb1caa80</t>
         </is>
       </c>
       <c r="H2" t="b">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:56:21+00:00</t>
+          <t>2026-09-17T03:05:14+00:00</t>
         </is>
       </c>
       <c r="K2" t="n">

--- a/results/sample-mock-run/benchmark_results.xlsx
+++ b/results/sample-mock-run/benchmark_results.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T03:05:01+00:00</t>
+          <t>2026-09-17T03:39:24+00:00</t>
         </is>
       </c>
     </row>
@@ -795,7 +795,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-17T03:05:14+00:00</t>
+          <t>2026-09-17T03:39:42+00:00</t>
         </is>
       </c>
       <c r="H2" s="3" t="n">
@@ -1154,17 +1154,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>run-20260917T030515-f5f4b29b</t>
+          <t>run-20260917T033943-24baba77</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T03:05:17+00:00</t>
+          <t>2026-09-17T03:39:46+00:00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-17T03:05:16+00:00</t>
+          <t>2026-09-17T03:39:43+00:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>62bd51cc58aff3b5128149c0e7098fc7bb1caa80</t>
+          <t>c12db6c91e7697f9dafc897de9c531e43921d60d</t>
         </is>
       </c>
       <c r="H2" t="b">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-17T03:05:14+00:00</t>
+          <t>2026-09-17T03:39:42+00:00</t>
         </is>
       </c>
       <c r="K2" t="n">

--- a/results/sample-mock-run/benchmark_results.xlsx
+++ b/results/sample-mock-run/benchmark_results.xlsx
@@ -475,48 +475,48 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Benchmark</t>
+          <t>Results as of (UTC)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>LLM summarization / hallucination / classification benchmark</t>
+          <t>2026-09-17T04:02:22+00:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Benchmark version</t>
+          <t>Benchmark</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>1.0.0</t>
+          <t>LLM summarization / hallucination / classification benchmark</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>API provider</t>
+          <t>Benchmark version</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>OpenRouter (every model, including judges)</t>
+          <t>1.0.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Generated at (UTC)</t>
+          <t>API provider</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T03:39:24+00:00</t>
+          <t>OpenRouter (every model, including judges)</t>
         </is>
       </c>
     </row>
@@ -795,7 +795,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-17T03:39:42+00:00</t>
+          <t>2026-09-17T04:02:17+00:00</t>
         </is>
       </c>
       <c r="H2" s="3" t="n">
@@ -1154,17 +1154,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>run-20260917T033943-24baba77</t>
+          <t>run-20260917T040219-d3b7a6c8</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T03:39:46+00:00</t>
+          <t>2026-09-17T04:02:22+00:00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-17T03:39:43+00:00</t>
+          <t>2026-09-17T04:02:19+00:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>c12db6c91e7697f9dafc897de9c531e43921d60d</t>
+          <t>a562a187d9fa8afca724f8c46c460ff7859af876</t>
         </is>
       </c>
       <c r="H2" t="b">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-17T03:39:42+00:00</t>
+          <t>2026-09-17T04:02:17+00:00</t>
         </is>
       </c>
       <c r="K2" t="n">

--- a/results/sample-mock-run/benchmark_results.xlsx
+++ b/results/sample-mock-run/benchmark_results.xlsx
@@ -480,7 +480,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T04:02:22+00:00</t>
+          <t>2026-09-17T08:16:15+00:00</t>
         </is>
       </c>
     </row>
@@ -795,7 +795,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-17T04:02:17+00:00</t>
+          <t>2026-09-17T08:16:12+00:00</t>
         </is>
       </c>
       <c r="H2" s="3" t="n">
@@ -1154,17 +1154,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>run-20260917T040219-d3b7a6c8</t>
+          <t>run-20260917T081613-42e8035e</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T04:02:22+00:00</t>
+          <t>2026-09-17T08:16:15+00:00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-17T04:02:19+00:00</t>
+          <t>2026-09-17T08:16:13+00:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>a562a187d9fa8afca724f8c46c460ff7859af876</t>
+          <t>a05631eb2e5769458bfd0e57d53515a08ebf6df1</t>
         </is>
       </c>
       <c r="H2" t="b">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-17T04:02:17+00:00</t>
+          <t>2026-09-17T08:16:12+00:00</t>
         </is>
       </c>
       <c r="K2" t="n">

--- a/results/sample-mock-run/benchmark_results.xlsx
+++ b/results/sample-mock-run/benchmark_results.xlsx
@@ -480,7 +480,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T08:16:15+00:00</t>
+          <t>2026-09-21T00:17:04+00:00</t>
         </is>
       </c>
     </row>
@@ -795,7 +795,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-17T08:16:12+00:00</t>
+          <t>2026-09-21T00:17:01+00:00</t>
         </is>
       </c>
       <c r="H2" s="3" t="n">
@@ -1154,17 +1154,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>run-20260917T081613-42e8035e</t>
+          <t>run-20260921T001702-87f3be61</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T08:16:15+00:00</t>
+          <t>2026-09-21T00:17:04+00:00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-17T08:16:13+00:00</t>
+          <t>2026-09-21T00:17:02+00:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>a05631eb2e5769458bfd0e57d53515a08ebf6df1</t>
+          <t>ad6a92fc3526efc27ceaa68d9e793b56fda72b88</t>
         </is>
       </c>
       <c r="H2" t="b">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-17T08:16:12+00:00</t>
+          <t>2026-09-21T00:17:01+00:00</t>
         </is>
       </c>
       <c r="K2" t="n">
